--- a/ListasDatos/Acevedo Rendón Ismael Arturo_2021.xlsx
+++ b/ListasDatos/Acevedo Rendón Ismael Arturo_2021.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24527"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\Estadis_cb192\archivos\ListasDatos\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F9F09BE-65AB-40E7-878D-809D881D72E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1DV" sheetId="1" r:id="rId1"/>
@@ -13,12 +19,12 @@
     <sheet name="3ASV" sheetId="4" r:id="rId4"/>
     <sheet name="5APV" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1155" uniqueCount="915">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="918">
   <si>
     <t>NC</t>
   </si>
@@ -641,9 +647,6 @@
     <t>2721149969</t>
   </si>
   <si>
-    <t>272207941q</t>
-  </si>
-  <si>
     <t>2721875959</t>
   </si>
   <si>
@@ -2763,13 +2766,25 @@
   </si>
   <si>
     <t>2722069450</t>
+  </si>
+  <si>
+    <t>Classroom</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>T</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2794,7 +2809,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -2817,13 +2832,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -2832,11 +2861,19 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -2878,7 +2915,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2910,9 +2947,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2944,6 +2999,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -3119,20 +3192,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K30"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" customWidth="1"/>
     <col min="2" max="4" width="20.7109375" customWidth="1"/>
-    <col min="5" max="5" width="35.7109375" customWidth="1"/>
-    <col min="6" max="7" width="15.7109375" customWidth="1"/>
-    <col min="8" max="8" width="50.7109375" customWidth="1"/>
-    <col min="9" max="9" width="35.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="35.7109375" hidden="1" customWidth="1"/>
+    <col min="6" max="7" width="15.7109375" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="50.7109375" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="35.7109375" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3163,8 +3236,11 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" s="2" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>21330051920110</v>
       </c>
@@ -3195,8 +3271,11 @@
       <c r="J2" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="3" spans="1:10">
+      <c r="K2" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>21330051920111</v>
       </c>
@@ -3224,8 +3303,11 @@
       <c r="J3" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="K3" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>21330051920112</v>
       </c>
@@ -3253,8 +3335,11 @@
       <c r="J4" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="5" spans="1:10">
+      <c r="K4" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>21330051920113</v>
       </c>
@@ -3282,11 +3367,14 @@
       <c r="I5" t="s">
         <v>187</v>
       </c>
-      <c r="J5" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="J5">
+        <v>272207941</v>
+      </c>
+      <c r="K5" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>21330051920114</v>
       </c>
@@ -3312,10 +3400,13 @@
         <v>188</v>
       </c>
       <c r="J6" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+        <v>207</v>
+      </c>
+      <c r="K6" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>21330051920115</v>
       </c>
@@ -3344,10 +3435,13 @@
         <v>189</v>
       </c>
       <c r="J7" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+        <v>208</v>
+      </c>
+      <c r="K7" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>21330051920116</v>
       </c>
@@ -3373,10 +3467,13 @@
         <v>190</v>
       </c>
       <c r="J8" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>209</v>
+      </c>
+      <c r="K8" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>21330051920117</v>
       </c>
@@ -3399,10 +3496,13 @@
         <v>164</v>
       </c>
       <c r="J9" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+        <v>210</v>
+      </c>
+      <c r="K9" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>21330051920118</v>
       </c>
@@ -3430,8 +3530,11 @@
       <c r="J10" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="11" spans="1:10">
+      <c r="K10" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>21330051920119</v>
       </c>
@@ -3457,10 +3560,13 @@
         <v>191</v>
       </c>
       <c r="J11" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>211</v>
+      </c>
+      <c r="K11" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>21330051920120</v>
       </c>
@@ -3486,10 +3592,13 @@
         <v>167</v>
       </c>
       <c r="J12" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>212</v>
+      </c>
+      <c r="K12" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>21330051920121</v>
       </c>
@@ -3518,10 +3627,13 @@
         <v>97</v>
       </c>
       <c r="J13" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+        <v>213</v>
+      </c>
+      <c r="K13" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>21330051920391</v>
       </c>
@@ -3547,10 +3659,13 @@
         <v>192</v>
       </c>
       <c r="J14" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+        <v>214</v>
+      </c>
+      <c r="K14" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>21330051920122</v>
       </c>
@@ -3581,8 +3696,11 @@
       <c r="J15" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="16" spans="1:10">
+      <c r="K15" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>21330051920123</v>
       </c>
@@ -3611,10 +3729,13 @@
         <v>194</v>
       </c>
       <c r="J16" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
+        <v>215</v>
+      </c>
+      <c r="K16" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>21330051920124</v>
       </c>
@@ -3643,10 +3764,13 @@
         <v>195</v>
       </c>
       <c r="J17" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+        <v>216</v>
+      </c>
+      <c r="K17" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>21330051920125</v>
       </c>
@@ -3677,8 +3801,11 @@
       <c r="J18" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="19" spans="1:10">
+      <c r="K18" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>21330051920126</v>
       </c>
@@ -3709,8 +3836,11 @@
       <c r="J19" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="20" spans="1:10">
+      <c r="K19" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>21330051920127</v>
       </c>
@@ -3739,10 +3869,13 @@
         <v>197</v>
       </c>
       <c r="J20" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+        <v>217</v>
+      </c>
+      <c r="K20" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20330051920275</v>
       </c>
@@ -3770,8 +3903,11 @@
       <c r="J21" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="22" spans="1:10">
+      <c r="K21" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21330051920128</v>
       </c>
@@ -3802,8 +3938,11 @@
       <c r="J22" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="23" spans="1:10">
+      <c r="K22" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>21330051920129</v>
       </c>
@@ -3831,8 +3970,11 @@
       <c r="J23" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="24" spans="1:10">
+      <c r="K23" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>21330051920130</v>
       </c>
@@ -3858,10 +4000,13 @@
         <v>108</v>
       </c>
       <c r="J24" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
+        <v>218</v>
+      </c>
+      <c r="K24" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>21330051920131</v>
       </c>
@@ -3890,10 +4035,13 @@
         <v>200</v>
       </c>
       <c r="J25" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
+        <v>219</v>
+      </c>
+      <c r="K25" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>18330051920377</v>
       </c>
@@ -3922,10 +4070,13 @@
         <v>201</v>
       </c>
       <c r="J26" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
+        <v>220</v>
+      </c>
+      <c r="K26" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>21330051920132</v>
       </c>
@@ -3951,10 +4102,13 @@
         <v>202</v>
       </c>
       <c r="J27" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
+        <v>221</v>
+      </c>
+      <c r="K27" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>20330051920152</v>
       </c>
@@ -3980,10 +4134,13 @@
         <v>203</v>
       </c>
       <c r="J28" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
+        <v>222</v>
+      </c>
+      <c r="K28" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>21330051920133</v>
       </c>
@@ -4012,10 +4169,13 @@
         <v>204</v>
       </c>
       <c r="J29" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
+        <v>223</v>
+      </c>
+      <c r="K29" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>21330051920134</v>
       </c>
@@ -4041,7 +4201,10 @@
         <v>205</v>
       </c>
       <c r="J30" t="s">
-        <v>225</v>
+        <v>224</v>
+      </c>
+      <c r="K30" t="s">
+        <v>917</v>
       </c>
     </row>
   </sheetData>
@@ -4050,20 +4213,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:K22"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
     <col min="2" max="4" width="20.7109375" customWidth="1"/>
-    <col min="5" max="5" width="35.7109375" customWidth="1"/>
-    <col min="6" max="7" width="15.7109375" customWidth="1"/>
-    <col min="8" max="8" width="50.7109375" customWidth="1"/>
-    <col min="9" max="9" width="35.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="35.7109375" hidden="1" customWidth="1"/>
+    <col min="6" max="7" width="15.7109375" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="50.7109375" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="35.7109375" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4094,40 +4257,46 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" s="2" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>21330051920135</v>
       </c>
       <c r="B2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C2" t="s">
         <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="J2" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>358</v>
+      </c>
+      <c r="K2" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>21330051920136</v>
       </c>
@@ -4135,89 +4304,98 @@
         <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="J3" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>359</v>
+      </c>
+      <c r="K3" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>21330051920137</v>
       </c>
       <c r="B4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C4" t="s">
         <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="J4" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>360</v>
+      </c>
+      <c r="K4" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>21330051920138</v>
       </c>
       <c r="B5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H5" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J5" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+        <v>291</v>
+      </c>
+      <c r="K5" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>21330051920139</v>
       </c>
@@ -4225,57 +4403,63 @@
         <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J6" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+        <v>311</v>
+      </c>
+      <c r="K6" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>21330051920140</v>
       </c>
       <c r="B7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F7" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="I7" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="J7" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+        <v>361</v>
+      </c>
+      <c r="K7" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>21330051920141</v>
       </c>
@@ -4283,31 +4467,34 @@
         <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E8" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F8" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G8" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H8" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="I8" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="J8" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>362</v>
+      </c>
+      <c r="K8" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>21330051920142</v>
       </c>
@@ -4315,31 +4502,34 @@
         <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D9" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F9" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="I9" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="J9" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+        <v>363</v>
+      </c>
+      <c r="K9" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>21330051920143</v>
       </c>
@@ -4347,153 +4537,168 @@
         <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H10" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="I10" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J10" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>295</v>
+      </c>
+      <c r="K10" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>21330051920381</v>
       </c>
       <c r="B11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C11" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D11" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H11" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="I11" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J11" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>296</v>
+      </c>
+      <c r="K11" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>21330051920144</v>
       </c>
       <c r="B12" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C12" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D12" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E12" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F12" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G12" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H12" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="I12" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="J12" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>316</v>
+      </c>
+      <c r="K12" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>21330051920145</v>
       </c>
       <c r="B13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C13" t="s">
         <v>21</v>
       </c>
       <c r="D13" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E13" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F13" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H13" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I13" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="J13" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+        <v>364</v>
+      </c>
+      <c r="K13" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>21330051920384</v>
       </c>
       <c r="B14" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C14" t="s">
         <v>49</v>
       </c>
       <c r="D14" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E14" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F14" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H14" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="I14" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J14" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+        <v>365</v>
+      </c>
+      <c r="K14" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>21330051920146</v>
       </c>
@@ -4501,60 +4706,66 @@
         <v>45</v>
       </c>
       <c r="C15" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D15" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E15" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F15" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G15" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H15" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="I15" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="J15" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+        <v>366</v>
+      </c>
+      <c r="K15" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>21330051920395</v>
       </c>
       <c r="B16" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C16" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E16" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F16" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H16" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="I16" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="J16" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
+        <v>367</v>
+      </c>
+      <c r="K16" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>21330051920147</v>
       </c>
@@ -4565,25 +4776,28 @@
         <v>20</v>
       </c>
       <c r="D17" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E17" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F17" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H17" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="I17" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="J17" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+        <v>302</v>
+      </c>
+      <c r="K17" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>21330051920148</v>
       </c>
@@ -4591,28 +4805,31 @@
         <v>31</v>
       </c>
       <c r="C18" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D18" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E18" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F18" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G18" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H18" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J18" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
+        <v>368</v>
+      </c>
+      <c r="K18" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>21330051920149</v>
       </c>
@@ -4623,25 +4840,28 @@
         <v>24</v>
       </c>
       <c r="D19" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E19" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F19" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G19" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H19" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="J19" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
+        <v>369</v>
+      </c>
+      <c r="K19" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>21330051920150</v>
       </c>
@@ -4649,86 +4869,95 @@
         <v>31</v>
       </c>
       <c r="C20" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D20" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E20" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F20" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H20" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="I20" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J20" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+        <v>305</v>
+      </c>
+      <c r="K20" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>21330051920382</v>
       </c>
       <c r="B21" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C21" t="s">
         <v>21</v>
       </c>
       <c r="D21" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E21" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F21" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H21" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="I21" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="J21" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
+        <v>370</v>
+      </c>
+      <c r="K21" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21330051920392</v>
       </c>
       <c r="B22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C22" t="s">
         <v>19</v>
       </c>
       <c r="D22" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E22" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F22" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G22" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H22" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="I22" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="J22" t="s">
-        <v>372</v>
+        <v>371</v>
+      </c>
+      <c r="K22" t="s">
+        <v>917</v>
       </c>
     </row>
   </sheetData>
@@ -4737,20 +4966,20 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:K22"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
     <col min="2" max="4" width="20.7109375" customWidth="1"/>
-    <col min="5" max="5" width="35.7109375" customWidth="1"/>
-    <col min="6" max="7" width="15.7109375" customWidth="1"/>
-    <col min="8" max="8" width="50.7109375" customWidth="1"/>
-    <col min="9" max="9" width="35.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="35.7109375" hidden="1" customWidth="1"/>
+    <col min="6" max="7" width="15.7109375" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="50.7109375" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="35.7109375" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4781,72 +5010,81 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" s="2" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>20330051920260</v>
       </c>
       <c r="B2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="G2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="I2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="J2" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>505</v>
+      </c>
+      <c r="K2" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>20330051920261</v>
       </c>
       <c r="B3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="G3" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H3" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="I3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="J3" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>454</v>
+      </c>
+      <c r="K3" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>19330051920314</v>
       </c>
@@ -4857,92 +5095,101 @@
         <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F4" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="I4" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="J4" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>506</v>
+      </c>
+      <c r="K4" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>20330051920262</v>
       </c>
       <c r="B5" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C5" t="s">
         <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E5" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F5" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="G5" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H5" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="I5" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="J5" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+        <v>507</v>
+      </c>
+      <c r="K5" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>20330051920264</v>
       </c>
       <c r="B6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C6" t="s">
         <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F6" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G6" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H6" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="I6" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="J6" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+        <v>508</v>
+      </c>
+      <c r="K6" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>20330051920267</v>
       </c>
@@ -4950,31 +5197,34 @@
         <v>44</v>
       </c>
       <c r="C7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D7" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E7" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F7" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="G7" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H7" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I7" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="J7" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+        <v>509</v>
+      </c>
+      <c r="K7" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>20330051920268</v>
       </c>
@@ -4985,57 +5235,63 @@
         <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E8" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="F8" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H8" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I8" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="J8" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>510</v>
+      </c>
+      <c r="K8" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>20330051920269</v>
       </c>
       <c r="B9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C9" t="s">
         <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E9" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="F9" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H9" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="I9" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="J9" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+        <v>511</v>
+      </c>
+      <c r="K9" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>20330051920270</v>
       </c>
@@ -5043,31 +5299,34 @@
         <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D10" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E10" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="F10" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G10" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H10" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="I10" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="J10" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>512</v>
+      </c>
+      <c r="K10" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>20330051920271</v>
       </c>
@@ -5075,28 +5334,31 @@
         <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D11" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F11" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H11" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="I11" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="J11" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>513</v>
+      </c>
+      <c r="K11" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>20330051920272</v>
       </c>
@@ -5104,57 +5366,63 @@
         <v>37</v>
       </c>
       <c r="C12" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D12" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E12" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F12" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H12" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="I12" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J12" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>514</v>
+      </c>
+      <c r="K12" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>19220030050208</v>
       </c>
       <c r="B13" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C13" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D13" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E13" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F13" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="G13" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H13" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="I13" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+        <v>497</v>
+      </c>
+      <c r="K13" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>20330051920273</v>
       </c>
@@ -5165,28 +5433,31 @@
         <v>18</v>
       </c>
       <c r="D14" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E14" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="F14" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="G14" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H14" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I14" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="J14" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+        <v>515</v>
+      </c>
+      <c r="K14" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>20330051920274</v>
       </c>
@@ -5197,86 +5468,95 @@
         <v>49</v>
       </c>
       <c r="D15" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E15" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="F15" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H15" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I15" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="J15" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+        <v>516</v>
+      </c>
+      <c r="K15" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>20330051920276</v>
       </c>
       <c r="B16" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C16" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D16" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E16" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="F16" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="G16" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H16" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="I16" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="J16" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
+        <v>517</v>
+      </c>
+      <c r="K16" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>19330051920238</v>
       </c>
       <c r="B17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C17" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D17" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E17" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="F17" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H17" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="I17" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="J17" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+        <v>518</v>
+      </c>
+      <c r="K17" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>20330051920278</v>
       </c>
@@ -5287,144 +5567,159 @@
         <v>57</v>
       </c>
       <c r="D18" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E18" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F18" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="G18" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H18" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I18" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="J18" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
+        <v>519</v>
+      </c>
+      <c r="K18" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>20330051920279</v>
       </c>
       <c r="B19" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C19" t="s">
         <v>31</v>
       </c>
       <c r="D19" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E19" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="F19" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="G19" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H19" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="I19" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="J19" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
+        <v>520</v>
+      </c>
+      <c r="K19" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>20330051920281</v>
       </c>
       <c r="B20" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C20" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D20" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E20" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F20" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G20" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H20" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="I20" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="J20" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+        <v>521</v>
+      </c>
+      <c r="K20" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20330051920282</v>
       </c>
       <c r="B21" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C21" t="s">
         <v>30</v>
       </c>
       <c r="D21" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E21" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F21" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H21" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="I21" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="J21" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
+        <v>522</v>
+      </c>
+      <c r="K21" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>19330051920425</v>
       </c>
       <c r="B22" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C22" t="s">
         <v>18</v>
       </c>
       <c r="D22" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E22" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F22" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="G22" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H22" t="s">
-        <v>486</v>
+        <v>485</v>
+      </c>
+      <c r="K22" t="s">
+        <v>915</v>
       </c>
     </row>
   </sheetData>
@@ -5433,20 +5728,20 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:K23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
     <col min="2" max="4" width="20.7109375" customWidth="1"/>
-    <col min="5" max="5" width="35.7109375" customWidth="1"/>
-    <col min="6" max="7" width="15.7109375" customWidth="1"/>
-    <col min="8" max="8" width="50.7109375" customWidth="1"/>
-    <col min="9" max="9" width="35.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="35.7109375" hidden="1" customWidth="1"/>
+    <col min="6" max="7" width="15.7109375" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="50.7109375" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="35.7109375" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5477,150 +5772,168 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" s="2" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>20330051920317</v>
       </c>
       <c r="B2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C2" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D2" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E2" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H2" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="I2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="J2" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>661</v>
+      </c>
+      <c r="K2" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>20330051920318</v>
       </c>
       <c r="B3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C3" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D3" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E3" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="F3" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G3" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H3" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="I3" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="J3" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>662</v>
+      </c>
+      <c r="K3" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>20330050470026</v>
       </c>
       <c r="B4" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C4" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D4" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="E4" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="F4" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H4" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="I4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J4" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>663</v>
+      </c>
+      <c r="K4" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>20330051920320</v>
       </c>
       <c r="B5" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C5" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D5" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E5" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="F5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H5" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="I5" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="J5" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+        <v>664</v>
+      </c>
+      <c r="K5" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>20330051920321</v>
       </c>
       <c r="B6" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C6" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D6" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E6" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F6" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="G6" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H6" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+        <v>625</v>
+      </c>
+      <c r="K6" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>20330051920322</v>
       </c>
@@ -5631,28 +5944,31 @@
         <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E7" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="F7" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="G7" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H7" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="I7" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="J7" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+        <v>665</v>
+      </c>
+      <c r="K7" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>20330051920323</v>
       </c>
@@ -5660,60 +5976,66 @@
         <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D8" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="E8" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="F8" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="G8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H8" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="I8" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="J8" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>666</v>
+      </c>
+      <c r="K8" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>20330051920380</v>
       </c>
       <c r="B9" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C9" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E9" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="F9" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H9" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="I9" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="J9" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+        <v>667</v>
+      </c>
+      <c r="K9" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>20330051920324</v>
       </c>
@@ -5724,28 +6046,31 @@
         <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="E10" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="F10" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="G10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H10" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="I10" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="J10" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>668</v>
+      </c>
+      <c r="K10" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>20330051920325</v>
       </c>
@@ -5753,63 +6078,69 @@
         <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D11" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="E11" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="F11" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="G11" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H11" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="I11" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="J11" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>669</v>
+      </c>
+      <c r="K11" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>20330051920397</v>
       </c>
       <c r="B12" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C12" t="s">
         <v>49</v>
       </c>
       <c r="D12" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E12" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="F12" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G12" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H12" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="I12" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="J12" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>670</v>
+      </c>
+      <c r="K12" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>20330051920326</v>
       </c>
@@ -5817,182 +6148,200 @@
         <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D13" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="E13" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="F13" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H13" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="I13" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="J13" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+        <v>671</v>
+      </c>
+      <c r="K13" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>20330051920327</v>
       </c>
       <c r="B14" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C14" t="s">
         <v>21</v>
       </c>
       <c r="D14" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E14" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="F14" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H14" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="I14" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="J14" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+        <v>672</v>
+      </c>
+      <c r="K14" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>20330051920328</v>
       </c>
       <c r="B15" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C15" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D15" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="E15" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="F15" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G15" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H15" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="I15" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="J15" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+        <v>673</v>
+      </c>
+      <c r="K15" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>20330051920396</v>
       </c>
       <c r="B16" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C16" t="s">
         <v>49</v>
       </c>
       <c r="D16" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E16" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="F16" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G16" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H16" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="I16" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="J16" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
+        <v>674</v>
+      </c>
+      <c r="K16" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>20330051920329</v>
       </c>
       <c r="B17" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C17" t="s">
         <v>42</v>
       </c>
       <c r="D17" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="E17" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="F17" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="G17" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H17" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="I17" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J17" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+        <v>675</v>
+      </c>
+      <c r="K17" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>20330051920330</v>
       </c>
       <c r="B18" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C18" t="s">
         <v>38</v>
       </c>
       <c r="D18" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E18" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="F18" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="G18" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H18" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="J18" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
+        <v>676</v>
+      </c>
+      <c r="K18" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>17330051920191</v>
       </c>
@@ -6000,150 +6349,165 @@
         <v>32</v>
       </c>
       <c r="C19" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D19" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E19" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="F19" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H19" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="I19" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="J19" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
+        <v>677</v>
+      </c>
+      <c r="K19" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>20330051920331</v>
       </c>
       <c r="B20" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C20" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D20" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E20" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="F20" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="G20" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="H20" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="I20" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="J20" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+        <v>678</v>
+      </c>
+      <c r="K20" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20330051920333</v>
       </c>
       <c r="B21" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C21" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D21" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E21" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="F21" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="G21" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H21" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="I21" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="J21" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
+        <v>679</v>
+      </c>
+      <c r="K21" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>20330051920334</v>
       </c>
       <c r="B22" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C22" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D22" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E22" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="F22" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="G22" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H22" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="I22" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="J22" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
+        <v>680</v>
+      </c>
+      <c r="K22" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>20330051920335</v>
       </c>
       <c r="B23" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C23" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D23" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E23" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="F23" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H23" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="I23" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="J23" t="s">
-        <v>682</v>
+        <v>681</v>
+      </c>
+      <c r="K23" t="s">
+        <v>917</v>
       </c>
     </row>
   </sheetData>
@@ -6152,20 +6516,20 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J39"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:K39"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
     <col min="2" max="4" width="20.7109375" customWidth="1"/>
-    <col min="5" max="5" width="35.7109375" customWidth="1"/>
-    <col min="6" max="7" width="15.7109375" customWidth="1"/>
-    <col min="8" max="8" width="50.7109375" customWidth="1"/>
-    <col min="9" max="9" width="35.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="35.7109375" hidden="1" customWidth="1"/>
+    <col min="6" max="7" width="15.7109375" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="50.7109375" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="35.7109375" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6196,40 +6560,46 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" s="2" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>19330051920307</v>
       </c>
       <c r="B2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="D2" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="E2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="F2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="G2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H2" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="I2" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="J2" t="s">
-        <v>886</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>885</v>
+      </c>
+      <c r="K2" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>19330051920308</v>
       </c>
@@ -6237,118 +6607,130 @@
         <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D3" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="E3" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="F3" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="G3" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H3" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="I3" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="J3" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>886</v>
+      </c>
+      <c r="K3" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>19330051920309</v>
       </c>
       <c r="B4" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C4" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="D4" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E4" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="F4" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="G4" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H4" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="I4" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="J4" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>821</v>
+      </c>
+      <c r="K4" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>19330051920311</v>
       </c>
       <c r="B5" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C5" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="D5" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E5" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F5" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H5" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="I5" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="J5" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+        <v>887</v>
+      </c>
+      <c r="K5" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>19330051920312</v>
       </c>
       <c r="B6" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C6" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="D6" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E6" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="F6" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="G6" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H6" t="s">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+        <v>831</v>
+      </c>
+      <c r="K6" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>19330051920316</v>
       </c>
@@ -6359,89 +6741,98 @@
         <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E7" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="F7" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="G7" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H7" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="I7" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="J7" t="s">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+        <v>888</v>
+      </c>
+      <c r="K7" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>19330051920450</v>
       </c>
       <c r="B8" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D8" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="E8" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="F8" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="G8" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H8" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="I8" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="J8" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>789</v>
+      </c>
+      <c r="K8" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>19330051920318</v>
       </c>
       <c r="B9" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C9" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D9" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="E9" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F9" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="H9" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="I9" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="J9" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+        <v>889</v>
+      </c>
+      <c r="K9" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>19330051920319</v>
       </c>
@@ -6449,51 +6840,57 @@
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D10" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="E10" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="F10" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="H10" t="s">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>835</v>
+      </c>
+      <c r="K10" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>19330051920323</v>
       </c>
       <c r="B11" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C11" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="D11" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="E11" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F11" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H11" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="I11" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="J11" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>890</v>
+      </c>
+      <c r="K11" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>19330051920441</v>
       </c>
@@ -6504,25 +6901,28 @@
         <v>10</v>
       </c>
       <c r="D12" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E12" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F12" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="G12" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H12" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="J12" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>891</v>
+      </c>
+      <c r="K12" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>19330051920325</v>
       </c>
@@ -6530,31 +6930,34 @@
         <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="D13" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="E13" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="F13" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="G13" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="H13" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="I13" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="J13" t="s">
-        <v>893</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+        <v>892</v>
+      </c>
+      <c r="K13" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>19330051920327</v>
       </c>
@@ -6562,31 +6965,34 @@
         <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="D14" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="E14" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="F14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="G14" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H14" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="I14" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="J14" t="s">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+        <v>893</v>
+      </c>
+      <c r="K14" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>19330051920453</v>
       </c>
@@ -6594,63 +7000,69 @@
         <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="D15" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="E15" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="F15" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="G15" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H15" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="I15" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="J15" t="s">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+        <v>893</v>
+      </c>
+      <c r="K15" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>19330051920321</v>
       </c>
       <c r="B16" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C16" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="D16" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="E16" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="F16" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="G16" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H16" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="I16" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="J16" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
+        <v>894</v>
+      </c>
+      <c r="K16" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>19330051920330</v>
       </c>
@@ -6658,28 +7070,31 @@
         <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="D17" t="s">
         <v>60</v>
       </c>
       <c r="E17" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="F17" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H17" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="I17" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="J17" t="s">
-        <v>896</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+        <v>895</v>
+      </c>
+      <c r="K17" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>19330051920332</v>
       </c>
@@ -6690,54 +7105,60 @@
         <v>44</v>
       </c>
       <c r="D18" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E18" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="F18" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="G18" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H18" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="J18" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
+        <v>896</v>
+      </c>
+      <c r="K18" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>19330051920331</v>
       </c>
       <c r="B19" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C19" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D19" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E19" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="F19" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H19" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="I19" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="J19" t="s">
-        <v>898</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
+        <v>897</v>
+      </c>
+      <c r="K19" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19330051920333</v>
       </c>
@@ -6748,57 +7169,63 @@
         <v>49</v>
       </c>
       <c r="D20" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="E20" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="F20" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="G20" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H20" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="I20" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="J20" t="s">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+        <v>898</v>
+      </c>
+      <c r="K20" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>19330051920334</v>
       </c>
       <c r="B21" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C21" t="s">
         <v>44</v>
       </c>
       <c r="D21" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="E21" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="F21" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H21" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="I21" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="J21" t="s">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
+        <v>899</v>
+      </c>
+      <c r="K21" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>19330051920337</v>
       </c>
@@ -6806,153 +7233,168 @@
         <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D22" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E22" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F22" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="G22" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H22" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="I22" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="J22" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
+        <v>900</v>
+      </c>
+      <c r="K22" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>19330051920338</v>
       </c>
       <c r="B23" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C23" t="s">
         <v>20</v>
       </c>
       <c r="D23" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E23" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="F23" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="G23" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H23" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="I23" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="J23" t="s">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
+        <v>901</v>
+      </c>
+      <c r="K23" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>19330051920339</v>
       </c>
       <c r="B24" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C24" t="s">
         <v>16</v>
       </c>
       <c r="D24" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E24" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="F24" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H24" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="J24" t="s">
-        <v>903</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
+        <v>902</v>
+      </c>
+      <c r="K24" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>19330051920340</v>
       </c>
       <c r="B25" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C25" t="s">
         <v>49</v>
       </c>
       <c r="D25" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="E25" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="F25" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="G25" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H25" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="I25" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="J25" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
+        <v>365</v>
+      </c>
+      <c r="K25" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>19330051920445</v>
       </c>
       <c r="B26" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C26" t="s">
         <v>21</v>
       </c>
       <c r="D26" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E26" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="F26" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="G26" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H26" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="I26" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="J26" t="s">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
+        <v>903</v>
+      </c>
+      <c r="K26" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>19330051920342</v>
       </c>
@@ -6960,54 +7402,60 @@
         <v>51</v>
       </c>
       <c r="C27" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="D27" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E27" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="F27" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H27" t="s">
-        <v>852</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
+        <v>851</v>
+      </c>
+      <c r="K27" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>19330051920341</v>
       </c>
       <c r="B28" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C28" t="s">
         <v>33</v>
       </c>
       <c r="D28" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="E28" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="F28" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="G28" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H28" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="I28" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="J28" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
+        <v>904</v>
+      </c>
+      <c r="K28" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>19330051920344</v>
       </c>
@@ -7015,185 +7463,203 @@
         <v>49</v>
       </c>
       <c r="C29" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D29" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="E29" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="F29" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H29" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="I29" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="J29" t="s">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
+        <v>905</v>
+      </c>
+      <c r="K29" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>19330051920347</v>
       </c>
       <c r="B30" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C30" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D30" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="E30" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="F30" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="G30" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="H30" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="I30" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="J30" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
+        <v>811</v>
+      </c>
+      <c r="K30" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>19330051920440</v>
       </c>
       <c r="B31" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C31" t="s">
         <v>21</v>
       </c>
       <c r="D31" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="E31" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="F31" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="G31" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H31" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="J31" t="s">
-        <v>907</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10">
+        <v>906</v>
+      </c>
+      <c r="K31" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>19330051920345</v>
       </c>
       <c r="B32" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C32" t="s">
         <v>24</v>
       </c>
       <c r="D32" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="E32" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="F32" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="G32" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="H32" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="I32" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="J32" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10">
+        <v>907</v>
+      </c>
+      <c r="K32" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>19330051920346</v>
       </c>
       <c r="B33" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C33" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D33" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E33" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="F33" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="G33" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H33" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="I33" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="J33" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10">
+        <v>908</v>
+      </c>
+      <c r="K33" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>19330051920350</v>
       </c>
       <c r="B34" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C34" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D34" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="E34" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="F34" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="G34" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="I34" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="J34" t="s">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10">
+        <v>909</v>
+      </c>
+      <c r="K34" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>19330051920351</v>
       </c>
@@ -7201,31 +7667,34 @@
         <v>33</v>
       </c>
       <c r="C35" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D35" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="E35" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="F35" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="G35" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="H35" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="I35" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="J35" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10">
+        <v>910</v>
+      </c>
+      <c r="K35" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>19330051920352</v>
       </c>
@@ -7236,22 +7705,25 @@
         <v>11</v>
       </c>
       <c r="D36" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="E36" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="F36" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H36" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="J36" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10">
+        <v>911</v>
+      </c>
+      <c r="K36" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>19330051920354</v>
       </c>
@@ -7262,51 +7734,57 @@
         <v>45</v>
       </c>
       <c r="D37" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="E37" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="F37" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="G37" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H37" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="I37" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="J37" t="s">
-        <v>913</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10">
+        <v>912</v>
+      </c>
+      <c r="K37" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>19330051920353</v>
       </c>
       <c r="B38" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C38" t="s">
         <v>30</v>
       </c>
       <c r="D38" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E38" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="F38" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H38" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10">
+        <v>862</v>
+      </c>
+      <c r="K38" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>19330051920355</v>
       </c>
@@ -7317,25 +7795,28 @@
         <v>57</v>
       </c>
       <c r="D39" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="E39" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="F39" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="G39" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H39" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="I39" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="J39" t="s">
-        <v>914</v>
+        <v>913</v>
+      </c>
+      <c r="K39" t="s">
+        <v>917</v>
       </c>
     </row>
   </sheetData>

--- a/ListasDatos/Acevedo Rendón Ismael Arturo_2021.xlsx
+++ b/ListasDatos/Acevedo Rendón Ismael Arturo_2021.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24527"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\Estadis_cb192\archivos\ListasDatos\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F9F09BE-65AB-40E7-878D-809D881D72E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="1DV" sheetId="1" r:id="rId1"/>
@@ -19,12 +13,12 @@
     <sheet name="3ASV" sheetId="4" r:id="rId4"/>
     <sheet name="5APV" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="918">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1155" uniqueCount="915">
   <si>
     <t>NC</t>
   </si>
@@ -647,6 +641,9 @@
     <t>2721149969</t>
   </si>
   <si>
+    <t>272207941q</t>
+  </si>
+  <si>
     <t>2721875959</t>
   </si>
   <si>
@@ -2766,25 +2763,13 @@
   </si>
   <si>
     <t>2722069450</t>
-  </si>
-  <si>
-    <t>Classroom</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>T</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2809,7 +2794,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -2832,27 +2817,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -2861,19 +2832,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -2915,7 +2878,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2947,27 +2910,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2999,24 +2944,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -3192,20 +3119,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J30"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.140625" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
     <col min="2" max="4" width="20.7109375" customWidth="1"/>
-    <col min="5" max="5" width="35.7109375" hidden="1" customWidth="1"/>
-    <col min="6" max="7" width="15.7109375" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="50.7109375" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="35.7109375" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="35.7109375" customWidth="1"/>
+    <col min="6" max="7" width="15.7109375" customWidth="1"/>
+    <col min="8" max="8" width="50.7109375" customWidth="1"/>
+    <col min="9" max="9" width="35.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3236,11 +3163,8 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2">
         <v>21330051920110</v>
       </c>
@@ -3271,11 +3195,8 @@
       <c r="J2" t="s">
         <v>115</v>
       </c>
-      <c r="K2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3">
         <v>21330051920111</v>
       </c>
@@ -3303,11 +3224,8 @@
       <c r="J3" t="s">
         <v>206</v>
       </c>
-      <c r="K3" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4">
         <v>21330051920112</v>
       </c>
@@ -3335,11 +3253,8 @@
       <c r="J4" t="s">
         <v>117</v>
       </c>
-      <c r="K4" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5">
         <v>21330051920113</v>
       </c>
@@ -3367,14 +3282,11 @@
       <c r="I5" t="s">
         <v>187</v>
       </c>
-      <c r="J5">
-        <v>272207941</v>
-      </c>
-      <c r="K5" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J5" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6">
         <v>21330051920114</v>
       </c>
@@ -3400,13 +3312,10 @@
         <v>188</v>
       </c>
       <c r="J6" t="s">
-        <v>207</v>
-      </c>
-      <c r="K6" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7">
         <v>21330051920115</v>
       </c>
@@ -3435,13 +3344,10 @@
         <v>189</v>
       </c>
       <c r="J7" t="s">
-        <v>208</v>
-      </c>
-      <c r="K7" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8">
         <v>21330051920116</v>
       </c>
@@ -3467,13 +3373,10 @@
         <v>190</v>
       </c>
       <c r="J8" t="s">
-        <v>209</v>
-      </c>
-      <c r="K8" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9">
         <v>21330051920117</v>
       </c>
@@ -3496,13 +3399,10 @@
         <v>164</v>
       </c>
       <c r="J9" t="s">
-        <v>210</v>
-      </c>
-      <c r="K9" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10">
         <v>21330051920118</v>
       </c>
@@ -3530,11 +3430,8 @@
       <c r="J10" t="s">
         <v>148</v>
       </c>
-      <c r="K10" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11">
         <v>21330051920119</v>
       </c>
@@ -3560,13 +3457,10 @@
         <v>191</v>
       </c>
       <c r="J11" t="s">
-        <v>211</v>
-      </c>
-      <c r="K11" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12">
         <v>21330051920120</v>
       </c>
@@ -3592,13 +3486,10 @@
         <v>167</v>
       </c>
       <c r="J12" t="s">
-        <v>212</v>
-      </c>
-      <c r="K12" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13">
         <v>21330051920121</v>
       </c>
@@ -3627,13 +3518,10 @@
         <v>97</v>
       </c>
       <c r="J13" t="s">
-        <v>213</v>
-      </c>
-      <c r="K13" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14">
         <v>21330051920391</v>
       </c>
@@ -3659,13 +3547,10 @@
         <v>192</v>
       </c>
       <c r="J14" t="s">
-        <v>214</v>
-      </c>
-      <c r="K14" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15">
         <v>21330051920122</v>
       </c>
@@ -3696,11 +3581,8 @@
       <c r="J15" t="s">
         <v>127</v>
       </c>
-      <c r="K15" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16">
         <v>21330051920123</v>
       </c>
@@ -3729,13 +3611,10 @@
         <v>194</v>
       </c>
       <c r="J16" t="s">
-        <v>215</v>
-      </c>
-      <c r="K16" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17">
         <v>21330051920124</v>
       </c>
@@ -3764,13 +3643,10 @@
         <v>195</v>
       </c>
       <c r="J17" t="s">
-        <v>216</v>
-      </c>
-      <c r="K17" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18">
         <v>21330051920125</v>
       </c>
@@ -3801,11 +3677,8 @@
       <c r="J18" t="s">
         <v>130</v>
       </c>
-      <c r="K18" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19">
         <v>21330051920126</v>
       </c>
@@ -3836,11 +3709,8 @@
       <c r="J19" t="s">
         <v>153</v>
       </c>
-      <c r="K19" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20">
         <v>21330051920127</v>
       </c>
@@ -3869,13 +3739,10 @@
         <v>197</v>
       </c>
       <c r="J20" t="s">
-        <v>217</v>
-      </c>
-      <c r="K20" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21">
         <v>20330051920275</v>
       </c>
@@ -3903,11 +3770,8 @@
       <c r="J21" t="s">
         <v>133</v>
       </c>
-      <c r="K21" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22">
         <v>21330051920128</v>
       </c>
@@ -3938,11 +3802,8 @@
       <c r="J22" t="s">
         <v>134</v>
       </c>
-      <c r="K22" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23">
         <v>21330051920129</v>
       </c>
@@ -3970,11 +3831,8 @@
       <c r="J23" t="s">
         <v>135</v>
       </c>
-      <c r="K23" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24">
         <v>21330051920130</v>
       </c>
@@ -4000,13 +3858,10 @@
         <v>108</v>
       </c>
       <c r="J24" t="s">
-        <v>218</v>
-      </c>
-      <c r="K24" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25">
         <v>21330051920131</v>
       </c>
@@ -4035,13 +3890,10 @@
         <v>200</v>
       </c>
       <c r="J25" t="s">
-        <v>219</v>
-      </c>
-      <c r="K25" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26">
         <v>18330051920377</v>
       </c>
@@ -4070,13 +3922,10 @@
         <v>201</v>
       </c>
       <c r="J26" t="s">
-        <v>220</v>
-      </c>
-      <c r="K26" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27">
         <v>21330051920132</v>
       </c>
@@ -4102,13 +3951,10 @@
         <v>202</v>
       </c>
       <c r="J27" t="s">
-        <v>221</v>
-      </c>
-      <c r="K27" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28">
         <v>20330051920152</v>
       </c>
@@ -4134,13 +3980,10 @@
         <v>203</v>
       </c>
       <c r="J28" t="s">
-        <v>222</v>
-      </c>
-      <c r="K28" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29">
         <v>21330051920133</v>
       </c>
@@ -4169,13 +4012,10 @@
         <v>204</v>
       </c>
       <c r="J29" t="s">
-        <v>223</v>
-      </c>
-      <c r="K29" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30">
         <v>21330051920134</v>
       </c>
@@ -4201,10 +4041,7 @@
         <v>205</v>
       </c>
       <c r="J30" t="s">
-        <v>224</v>
-      </c>
-      <c r="K30" t="s">
-        <v>917</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>
@@ -4213,20 +4050,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J22"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
     <col min="2" max="4" width="20.7109375" customWidth="1"/>
-    <col min="5" max="5" width="35.7109375" hidden="1" customWidth="1"/>
-    <col min="6" max="7" width="15.7109375" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="50.7109375" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="35.7109375" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="35.7109375" customWidth="1"/>
+    <col min="6" max="7" width="15.7109375" customWidth="1"/>
+    <col min="8" max="8" width="50.7109375" customWidth="1"/>
+    <col min="9" max="9" width="35.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4257,46 +4094,40 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2">
         <v>21330051920135</v>
       </c>
       <c r="B2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C2" t="s">
         <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="I2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J2" t="s">
-        <v>358</v>
-      </c>
-      <c r="K2" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3">
         <v>21330051920136</v>
       </c>
@@ -4304,98 +4135,89 @@
         <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="J3" t="s">
-        <v>359</v>
-      </c>
-      <c r="K3" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4">
         <v>21330051920137</v>
       </c>
       <c r="B4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C4" t="s">
         <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J4" t="s">
-        <v>360</v>
-      </c>
-      <c r="K4" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5">
         <v>21330051920138</v>
       </c>
       <c r="B5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C5" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F5" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H5" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J5" t="s">
-        <v>291</v>
-      </c>
-      <c r="K5" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6">
         <v>21330051920139</v>
       </c>
@@ -4403,63 +4225,57 @@
         <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="J6" t="s">
-        <v>311</v>
-      </c>
-      <c r="K6" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7">
         <v>21330051920140</v>
       </c>
       <c r="B7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E7" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F7" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I7" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="J7" t="s">
-        <v>361</v>
-      </c>
-      <c r="K7" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8">
         <v>21330051920141</v>
       </c>
@@ -4467,34 +4283,31 @@
         <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G8" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H8" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I8" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J8" t="s">
-        <v>362</v>
-      </c>
-      <c r="K8" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9">
         <v>21330051920142</v>
       </c>
@@ -4502,34 +4315,31 @@
         <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G9" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J9" t="s">
-        <v>363</v>
-      </c>
-      <c r="K9" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10">
         <v>21330051920143</v>
       </c>
@@ -4537,168 +4347,153 @@
         <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="G10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="I10" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J10" t="s">
-        <v>295</v>
-      </c>
-      <c r="K10" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11">
         <v>21330051920381</v>
       </c>
       <c r="B11" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D11" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H11" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I11" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J11" t="s">
-        <v>296</v>
-      </c>
-      <c r="K11" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12">
         <v>21330051920144</v>
       </c>
       <c r="B12" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C12" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D12" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E12" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F12" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G12" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="I12" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J12" t="s">
-        <v>316</v>
-      </c>
-      <c r="K12" t="s">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13">
         <v>21330051920145</v>
       </c>
       <c r="B13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C13" t="s">
         <v>21</v>
       </c>
       <c r="D13" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E13" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F13" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H13" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="I13" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="J13" t="s">
-        <v>364</v>
-      </c>
-      <c r="K13" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14">
         <v>21330051920384</v>
       </c>
       <c r="B14" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C14" t="s">
         <v>49</v>
       </c>
       <c r="D14" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E14" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F14" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="I14" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="J14" t="s">
-        <v>365</v>
-      </c>
-      <c r="K14" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15">
         <v>21330051920146</v>
       </c>
@@ -4706,66 +4501,60 @@
         <v>45</v>
       </c>
       <c r="C15" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D15" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E15" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F15" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G15" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H15" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="I15" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="J15" t="s">
-        <v>366</v>
-      </c>
-      <c r="K15" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16">
         <v>21330051920395</v>
       </c>
       <c r="B16" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C16" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D16" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E16" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F16" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H16" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="I16" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="J16" t="s">
-        <v>367</v>
-      </c>
-      <c r="K16" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17">
         <v>21330051920147</v>
       </c>
@@ -4776,28 +4565,25 @@
         <v>20</v>
       </c>
       <c r="D17" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E17" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F17" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H17" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="I17" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="J17" t="s">
-        <v>302</v>
-      </c>
-      <c r="K17" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18">
         <v>21330051920148</v>
       </c>
@@ -4805,31 +4591,28 @@
         <v>31</v>
       </c>
       <c r="C18" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D18" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E18" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F18" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G18" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H18" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="J18" t="s">
-        <v>368</v>
-      </c>
-      <c r="K18" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19">
         <v>21330051920149</v>
       </c>
@@ -4840,28 +4623,25 @@
         <v>24</v>
       </c>
       <c r="D19" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E19" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F19" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G19" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H19" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="J19" t="s">
-        <v>369</v>
-      </c>
-      <c r="K19" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20">
         <v>21330051920150</v>
       </c>
@@ -4869,95 +4649,86 @@
         <v>31</v>
       </c>
       <c r="C20" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D20" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E20" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F20" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H20" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I20" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J20" t="s">
-        <v>305</v>
-      </c>
-      <c r="K20" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21">
         <v>21330051920382</v>
       </c>
       <c r="B21" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C21" t="s">
         <v>21</v>
       </c>
       <c r="D21" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E21" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F21" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H21" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="I21" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="J21" t="s">
-        <v>370</v>
-      </c>
-      <c r="K21" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22">
         <v>21330051920392</v>
       </c>
       <c r="B22" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C22" t="s">
         <v>19</v>
       </c>
       <c r="D22" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E22" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F22" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G22" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H22" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="I22" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="J22" t="s">
-        <v>371</v>
-      </c>
-      <c r="K22" t="s">
-        <v>917</v>
+        <v>372</v>
       </c>
     </row>
   </sheetData>
@@ -4966,20 +4737,20 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J22"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
     <col min="2" max="4" width="20.7109375" customWidth="1"/>
-    <col min="5" max="5" width="35.7109375" hidden="1" customWidth="1"/>
-    <col min="6" max="7" width="15.7109375" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="50.7109375" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="35.7109375" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="35.7109375" customWidth="1"/>
+    <col min="6" max="7" width="15.7109375" customWidth="1"/>
+    <col min="8" max="8" width="50.7109375" customWidth="1"/>
+    <col min="9" max="9" width="35.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5010,81 +4781,72 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2">
         <v>20330051920260</v>
       </c>
       <c r="B2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="G2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H2" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="I2" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="J2" t="s">
-        <v>505</v>
-      </c>
-      <c r="K2" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3">
         <v>20330051920261</v>
       </c>
       <c r="B3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C3" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H3" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="I3" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="J3" t="s">
-        <v>454</v>
-      </c>
-      <c r="K3" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4">
         <v>19330051920314</v>
       </c>
@@ -5095,101 +4857,92 @@
         <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F4" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G4" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H4" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="I4" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="J4" t="s">
-        <v>506</v>
-      </c>
-      <c r="K4" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5">
         <v>20330051920262</v>
       </c>
       <c r="B5" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C5" t="s">
         <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E5" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F5" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="G5" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H5" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="I5" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="J5" t="s">
-        <v>507</v>
-      </c>
-      <c r="K5" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6">
         <v>20330051920264</v>
       </c>
       <c r="B6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C6" t="s">
         <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E6" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F6" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G6" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H6" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="I6" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="J6" t="s">
-        <v>508</v>
-      </c>
-      <c r="K6" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7">
         <v>20330051920267</v>
       </c>
@@ -5197,34 +4950,31 @@
         <v>44</v>
       </c>
       <c r="C7" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D7" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E7" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F7" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="G7" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H7" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="I7" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="J7" t="s">
-        <v>509</v>
-      </c>
-      <c r="K7" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8">
         <v>20330051920268</v>
       </c>
@@ -5235,63 +4985,57 @@
         <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F8" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="G8" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H8" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="I8" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="J8" t="s">
-        <v>510</v>
-      </c>
-      <c r="K8" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9">
         <v>20330051920269</v>
       </c>
       <c r="B9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C9" t="s">
         <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E9" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F9" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H9" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I9" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="J9" t="s">
-        <v>511</v>
-      </c>
-      <c r="K9" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10">
         <v>20330051920270</v>
       </c>
@@ -5299,34 +5043,31 @@
         <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D10" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E10" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F10" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="G10" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H10" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="I10" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="J10" t="s">
-        <v>512</v>
-      </c>
-      <c r="K10" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11">
         <v>20330051920271</v>
       </c>
@@ -5334,31 +5075,28 @@
         <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E11" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F11" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H11" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="I11" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="J11" t="s">
-        <v>513</v>
-      </c>
-      <c r="K11" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12">
         <v>20330051920272</v>
       </c>
@@ -5366,63 +5104,57 @@
         <v>37</v>
       </c>
       <c r="C12" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D12" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E12" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F12" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H12" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I12" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="J12" t="s">
-        <v>514</v>
-      </c>
-      <c r="K12" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13">
         <v>19220030050208</v>
       </c>
       <c r="B13" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C13" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D13" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E13" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F13" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G13" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H13" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="I13" t="s">
-        <v>497</v>
-      </c>
-      <c r="K13" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14">
         <v>20330051920273</v>
       </c>
@@ -5433,31 +5165,28 @@
         <v>18</v>
       </c>
       <c r="D14" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E14" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F14" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G14" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H14" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="I14" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="J14" t="s">
-        <v>515</v>
-      </c>
-      <c r="K14" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15">
         <v>20330051920274</v>
       </c>
@@ -5468,95 +5197,86 @@
         <v>49</v>
       </c>
       <c r="D15" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E15" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F15" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H15" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="I15" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="J15" t="s">
-        <v>516</v>
-      </c>
-      <c r="K15" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16">
         <v>20330051920276</v>
       </c>
       <c r="B16" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C16" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D16" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E16" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F16" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G16" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H16" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I16" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="J16" t="s">
-        <v>517</v>
-      </c>
-      <c r="K16" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17">
         <v>19330051920238</v>
       </c>
       <c r="B17" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C17" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D17" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E17" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F17" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H17" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I17" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="J17" t="s">
-        <v>518</v>
-      </c>
-      <c r="K17" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18">
         <v>20330051920278</v>
       </c>
@@ -5567,159 +5287,144 @@
         <v>57</v>
       </c>
       <c r="D18" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E18" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F18" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G18" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H18" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="I18" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="J18" t="s">
-        <v>519</v>
-      </c>
-      <c r="K18" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19">
         <v>20330051920279</v>
       </c>
       <c r="B19" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C19" t="s">
         <v>31</v>
       </c>
       <c r="D19" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E19" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F19" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="G19" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H19" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="I19" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="J19" t="s">
-        <v>520</v>
-      </c>
-      <c r="K19" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20">
         <v>20330051920281</v>
       </c>
       <c r="B20" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C20" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D20" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E20" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F20" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G20" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H20" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="I20" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="J20" t="s">
-        <v>521</v>
-      </c>
-      <c r="K20" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21">
         <v>20330051920282</v>
       </c>
       <c r="B21" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C21" t="s">
         <v>30</v>
       </c>
       <c r="D21" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E21" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F21" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H21" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="I21" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="J21" t="s">
-        <v>522</v>
-      </c>
-      <c r="K21" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22">
         <v>19330051920425</v>
       </c>
       <c r="B22" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C22" t="s">
         <v>18</v>
       </c>
       <c r="D22" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E22" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F22" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="G22" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H22" t="s">
-        <v>485</v>
-      </c>
-      <c r="K22" t="s">
-        <v>915</v>
+        <v>486</v>
       </c>
     </row>
   </sheetData>
@@ -5728,20 +5433,20 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:K23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J23"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
     <col min="2" max="4" width="20.7109375" customWidth="1"/>
-    <col min="5" max="5" width="35.7109375" hidden="1" customWidth="1"/>
-    <col min="6" max="7" width="15.7109375" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="50.7109375" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="35.7109375" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="35.7109375" customWidth="1"/>
+    <col min="6" max="7" width="15.7109375" customWidth="1"/>
+    <col min="8" max="8" width="50.7109375" customWidth="1"/>
+    <col min="9" max="9" width="35.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5772,168 +5477,150 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2">
         <v>20330051920317</v>
       </c>
       <c r="B2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D2" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E2" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H2" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="I2" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="J2" t="s">
-        <v>661</v>
-      </c>
-      <c r="K2" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3">
         <v>20330051920318</v>
       </c>
       <c r="B3" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C3" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D3" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E3" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="F3" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="G3" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H3" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="I3" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="J3" t="s">
-        <v>662</v>
-      </c>
-      <c r="K3" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4">
         <v>20330050470026</v>
       </c>
       <c r="B4" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C4" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D4" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E4" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="F4" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H4" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="I4" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="J4" t="s">
-        <v>663</v>
-      </c>
-      <c r="K4" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5">
         <v>20330051920320</v>
       </c>
       <c r="B5" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C5" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D5" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E5" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="F5" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H5" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="I5" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="J5" t="s">
-        <v>664</v>
-      </c>
-      <c r="K5" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6">
         <v>20330051920321</v>
       </c>
       <c r="B6" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C6" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D6" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E6" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="F6" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="G6" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H6" t="s">
-        <v>625</v>
-      </c>
-      <c r="K6" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7">
         <v>20330051920322</v>
       </c>
@@ -5944,31 +5631,28 @@
         <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E7" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F7" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="G7" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H7" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="I7" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="J7" t="s">
-        <v>665</v>
-      </c>
-      <c r="K7" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8">
         <v>20330051920323</v>
       </c>
@@ -5976,66 +5660,60 @@
         <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D8" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E8" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="F8" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="G8" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H8" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="I8" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="J8" t="s">
-        <v>666</v>
-      </c>
-      <c r="K8" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9">
         <v>20330051920380</v>
       </c>
       <c r="B9" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C9" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E9" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="F9" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H9" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="I9" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="J9" t="s">
-        <v>667</v>
-      </c>
-      <c r="K9" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10">
         <v>20330051920324</v>
       </c>
@@ -6046,31 +5724,28 @@
         <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E10" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="F10" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="G10" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H10" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="I10" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="J10" t="s">
-        <v>668</v>
-      </c>
-      <c r="K10" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11">
         <v>20330051920325</v>
       </c>
@@ -6078,69 +5753,63 @@
         <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D11" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="E11" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="F11" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="G11" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H11" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="I11" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="J11" t="s">
-        <v>669</v>
-      </c>
-      <c r="K11" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12">
         <v>20330051920397</v>
       </c>
       <c r="B12" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C12" t="s">
         <v>49</v>
       </c>
       <c r="D12" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E12" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F12" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="G12" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H12" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="I12" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="J12" t="s">
-        <v>670</v>
-      </c>
-      <c r="K12" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13">
         <v>20330051920326</v>
       </c>
@@ -6148,200 +5817,182 @@
         <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D13" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="E13" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="F13" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="I13" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="J13" t="s">
-        <v>671</v>
-      </c>
-      <c r="K13" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14">
         <v>20330051920327</v>
       </c>
       <c r="B14" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C14" t="s">
         <v>21</v>
       </c>
       <c r="D14" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E14" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="F14" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H14" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="I14" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="J14" t="s">
-        <v>672</v>
-      </c>
-      <c r="K14" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15">
         <v>20330051920328</v>
       </c>
       <c r="B15" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C15" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D15" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E15" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="F15" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="G15" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H15" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="I15" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="J15" t="s">
-        <v>673</v>
-      </c>
-      <c r="K15" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16">
         <v>20330051920396</v>
       </c>
       <c r="B16" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C16" t="s">
         <v>49</v>
       </c>
       <c r="D16" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E16" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="F16" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="G16" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H16" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="I16" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="J16" t="s">
-        <v>674</v>
-      </c>
-      <c r="K16" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17">
         <v>20330051920329</v>
       </c>
       <c r="B17" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C17" t="s">
         <v>42</v>
       </c>
       <c r="D17" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E17" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="F17" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="G17" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H17" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="I17" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="J17" t="s">
-        <v>675</v>
-      </c>
-      <c r="K17" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18">
         <v>20330051920330</v>
       </c>
       <c r="B18" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C18" t="s">
         <v>38</v>
       </c>
       <c r="D18" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E18" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F18" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="G18" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H18" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="J18" t="s">
-        <v>676</v>
-      </c>
-      <c r="K18" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19">
         <v>17330051920191</v>
       </c>
@@ -6349,165 +6000,150 @@
         <v>32</v>
       </c>
       <c r="C19" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D19" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E19" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="F19" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H19" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="I19" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="J19" t="s">
-        <v>677</v>
-      </c>
-      <c r="K19" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20">
         <v>20330051920331</v>
       </c>
       <c r="B20" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C20" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D20" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="E20" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F20" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="G20" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H20" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="I20" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="J20" t="s">
-        <v>678</v>
-      </c>
-      <c r="K20" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21">
         <v>20330051920333</v>
       </c>
       <c r="B21" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C21" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D21" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E21" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="F21" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="G21" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H21" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="I21" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="J21" t="s">
-        <v>679</v>
-      </c>
-      <c r="K21" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22">
         <v>20330051920334</v>
       </c>
       <c r="B22" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C22" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D22" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E22" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="F22" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="G22" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H22" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="I22" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="J22" t="s">
-        <v>680</v>
-      </c>
-      <c r="K22" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23">
         <v>20330051920335</v>
       </c>
       <c r="B23" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C23" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D23" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E23" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="F23" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H23" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="I23" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="J23" t="s">
-        <v>681</v>
-      </c>
-      <c r="K23" t="s">
-        <v>917</v>
+        <v>682</v>
       </c>
     </row>
   </sheetData>
@@ -6516,20 +6152,20 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:K39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
     <col min="2" max="4" width="20.7109375" customWidth="1"/>
-    <col min="5" max="5" width="35.7109375" hidden="1" customWidth="1"/>
-    <col min="6" max="7" width="15.7109375" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="50.7109375" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="35.7109375" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="35.7109375" customWidth="1"/>
+    <col min="6" max="7" width="15.7109375" customWidth="1"/>
+    <col min="8" max="8" width="50.7109375" customWidth="1"/>
+    <col min="9" max="9" width="35.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6560,46 +6196,40 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2">
         <v>19330051920307</v>
       </c>
       <c r="B2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C2" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="D2" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="E2" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="F2" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="G2" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="I2" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="J2" t="s">
-        <v>885</v>
-      </c>
-      <c r="K2" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3">
         <v>19330051920308</v>
       </c>
@@ -6607,130 +6237,118 @@
         <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D3" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E3" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="F3" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="G3" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H3" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="I3" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="J3" t="s">
-        <v>886</v>
-      </c>
-      <c r="K3" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4">
         <v>19330051920309</v>
       </c>
       <c r="B4" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C4" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D4" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="E4" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="F4" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="G4" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H4" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="I4" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="J4" t="s">
-        <v>821</v>
-      </c>
-      <c r="K4" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5">
         <v>19330051920311</v>
       </c>
       <c r="B5" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C5" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="D5" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="E5" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="F5" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H5" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="I5" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="J5" t="s">
-        <v>887</v>
-      </c>
-      <c r="K5" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6">
         <v>19330051920312</v>
       </c>
       <c r="B6" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C6" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="D6" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="E6" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="F6" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="G6" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H6" t="s">
-        <v>831</v>
-      </c>
-      <c r="K6" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7">
         <v>19330051920316</v>
       </c>
@@ -6741,98 +6359,89 @@
         <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="E7" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="F7" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="G7" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H7" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="I7" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="J7" t="s">
-        <v>888</v>
-      </c>
-      <c r="K7" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8">
         <v>19330051920450</v>
       </c>
       <c r="B8" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D8" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="E8" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="F8" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="G8" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H8" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="I8" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="J8" t="s">
-        <v>789</v>
-      </c>
-      <c r="K8" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9">
         <v>19330051920318</v>
       </c>
       <c r="B9" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C9" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D9" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="E9" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="F9" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H9" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="I9" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="J9" t="s">
-        <v>889</v>
-      </c>
-      <c r="K9" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10">
         <v>19330051920319</v>
       </c>
@@ -6840,57 +6449,51 @@
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="D10" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="E10" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="F10" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H10" t="s">
-        <v>835</v>
-      </c>
-      <c r="K10" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11">
         <v>19330051920323</v>
       </c>
       <c r="B11" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C11" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="D11" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="E11" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="F11" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H11" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="I11" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="J11" t="s">
-        <v>890</v>
-      </c>
-      <c r="K11" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12">
         <v>19330051920441</v>
       </c>
@@ -6901,28 +6504,25 @@
         <v>10</v>
       </c>
       <c r="D12" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E12" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="F12" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="G12" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H12" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="J12" t="s">
-        <v>891</v>
-      </c>
-      <c r="K12" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13">
         <v>19330051920325</v>
       </c>
@@ -6930,34 +6530,31 @@
         <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="D13" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="E13" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="F13" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="G13" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H13" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="I13" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="J13" t="s">
-        <v>892</v>
-      </c>
-      <c r="K13" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14">
         <v>19330051920327</v>
       </c>
@@ -6965,34 +6562,31 @@
         <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D14" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="E14" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="F14" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="G14" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H14" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="I14" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="J14" t="s">
-        <v>893</v>
-      </c>
-      <c r="K14" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15">
         <v>19330051920453</v>
       </c>
@@ -7000,69 +6594,63 @@
         <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D15" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="E15" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="F15" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="G15" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H15" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="I15" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="J15" t="s">
-        <v>893</v>
-      </c>
-      <c r="K15" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16">
         <v>19330051920321</v>
       </c>
       <c r="B16" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C16" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="D16" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="E16" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="F16" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="G16" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H16" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="I16" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="J16" t="s">
-        <v>894</v>
-      </c>
-      <c r="K16" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17">
         <v>19330051920330</v>
       </c>
@@ -7070,31 +6658,28 @@
         <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="D17" t="s">
         <v>60</v>
       </c>
       <c r="E17" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="F17" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H17" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="I17" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="J17" t="s">
-        <v>895</v>
-      </c>
-      <c r="K17" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18">
         <v>19330051920332</v>
       </c>
@@ -7105,60 +6690,54 @@
         <v>44</v>
       </c>
       <c r="D18" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="E18" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="F18" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="G18" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H18" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="J18" t="s">
-        <v>896</v>
-      </c>
-      <c r="K18" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19">
         <v>19330051920331</v>
       </c>
       <c r="B19" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C19" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D19" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E19" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="F19" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H19" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="I19" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="J19" t="s">
-        <v>897</v>
-      </c>
-      <c r="K19" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20">
         <v>19330051920333</v>
       </c>
@@ -7169,63 +6748,57 @@
         <v>49</v>
       </c>
       <c r="D20" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="E20" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="F20" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G20" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H20" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="I20" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="J20" t="s">
-        <v>898</v>
-      </c>
-      <c r="K20" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21">
         <v>19330051920334</v>
       </c>
       <c r="B21" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C21" t="s">
         <v>44</v>
       </c>
       <c r="D21" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="E21" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="F21" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H21" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="I21" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="J21" t="s">
-        <v>899</v>
-      </c>
-      <c r="K21" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22">
         <v>19330051920337</v>
       </c>
@@ -7233,168 +6806,153 @@
         <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D22" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="E22" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="F22" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="G22" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H22" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="I22" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="J22" t="s">
-        <v>900</v>
-      </c>
-      <c r="K22" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23">
         <v>19330051920338</v>
       </c>
       <c r="B23" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C23" t="s">
         <v>20</v>
       </c>
       <c r="D23" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="E23" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="F23" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="G23" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H23" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="I23" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J23" t="s">
-        <v>901</v>
-      </c>
-      <c r="K23" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24">
         <v>19330051920339</v>
       </c>
       <c r="B24" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C24" t="s">
         <v>16</v>
       </c>
       <c r="D24" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E24" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="F24" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H24" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="J24" t="s">
-        <v>902</v>
-      </c>
-      <c r="K24" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25">
         <v>19330051920340</v>
       </c>
       <c r="B25" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C25" t="s">
         <v>49</v>
       </c>
       <c r="D25" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="E25" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="F25" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="G25" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H25" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="I25" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="J25" t="s">
-        <v>365</v>
-      </c>
-      <c r="K25" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26">
         <v>19330051920445</v>
       </c>
       <c r="B26" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C26" t="s">
         <v>21</v>
       </c>
       <c r="D26" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="E26" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="F26" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="G26" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H26" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="I26" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="J26" t="s">
-        <v>903</v>
-      </c>
-      <c r="K26" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27">
         <v>19330051920342</v>
       </c>
@@ -7402,60 +6960,54 @@
         <v>51</v>
       </c>
       <c r="C27" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="D27" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="E27" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="F27" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H27" t="s">
-        <v>851</v>
-      </c>
-      <c r="K27" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28">
         <v>19330051920341</v>
       </c>
       <c r="B28" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C28" t="s">
         <v>33</v>
       </c>
       <c r="D28" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="E28" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="F28" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="G28" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H28" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="I28" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="J28" t="s">
-        <v>904</v>
-      </c>
-      <c r="K28" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29">
         <v>19330051920344</v>
       </c>
@@ -7463,203 +7015,185 @@
         <v>49</v>
       </c>
       <c r="C29" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D29" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="E29" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="F29" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H29" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="I29" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="J29" t="s">
-        <v>905</v>
-      </c>
-      <c r="K29" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30">
         <v>19330051920347</v>
       </c>
       <c r="B30" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C30" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D30" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="E30" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="F30" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="G30" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H30" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="I30" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="J30" t="s">
-        <v>811</v>
-      </c>
-      <c r="K30" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31">
         <v>19330051920440</v>
       </c>
       <c r="B31" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C31" t="s">
         <v>21</v>
       </c>
       <c r="D31" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="E31" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="F31" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="G31" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H31" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="J31" t="s">
-        <v>906</v>
-      </c>
-      <c r="K31" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32">
         <v>19330051920345</v>
       </c>
       <c r="B32" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C32" t="s">
         <v>24</v>
       </c>
       <c r="D32" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="E32" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="F32" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="G32" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="H32" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="I32" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="J32" t="s">
-        <v>907</v>
-      </c>
-      <c r="K32" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
       <c r="A33">
         <v>19330051920346</v>
       </c>
       <c r="B33" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C33" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D33" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="E33" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="F33" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="G33" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H33" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="I33" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="J33" t="s">
-        <v>908</v>
-      </c>
-      <c r="K33" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34">
         <v>19330051920350</v>
       </c>
       <c r="B34" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C34" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D34" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="E34" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="F34" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="G34" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H34" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="I34" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="J34" t="s">
-        <v>909</v>
-      </c>
-      <c r="K34" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35">
         <v>19330051920351</v>
       </c>
@@ -7667,34 +7201,31 @@
         <v>33</v>
       </c>
       <c r="C35" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D35" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="E35" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="F35" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="G35" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H35" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="I35" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="J35" t="s">
-        <v>910</v>
-      </c>
-      <c r="K35" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
       <c r="A36">
         <v>19330051920352</v>
       </c>
@@ -7705,25 +7236,22 @@
         <v>11</v>
       </c>
       <c r="D36" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="E36" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="F36" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H36" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="J36" t="s">
-        <v>911</v>
-      </c>
-      <c r="K36" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37">
         <v>19330051920354</v>
       </c>
@@ -7734,57 +7262,51 @@
         <v>45</v>
       </c>
       <c r="D37" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="E37" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="F37" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="G37" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H37" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="I37" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="J37" t="s">
-        <v>912</v>
-      </c>
-      <c r="K37" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38">
         <v>19330051920353</v>
       </c>
       <c r="B38" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C38" t="s">
         <v>30</v>
       </c>
       <c r="D38" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="E38" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="F38" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H38" t="s">
-        <v>862</v>
-      </c>
-      <c r="K38" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39">
         <v>19330051920355</v>
       </c>
@@ -7795,28 +7317,25 @@
         <v>57</v>
       </c>
       <c r="D39" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="E39" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="F39" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="G39" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H39" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="I39" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="J39" t="s">
-        <v>913</v>
-      </c>
-      <c r="K39" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
     </row>
   </sheetData>
